--- a/forms/trg/Formulir_TRG_posbrg.xlsx
+++ b/forms/trg/Formulir_TRG_posbrg.xlsx
@@ -686,7 +686,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Keahlian anggota banyak yang kosong. Mohon pilih keahlian utama untuk setiap anggota.</t>
+          <t>Data TRG ini relatif lengkap. Mohon periksa dan lengkapi mitra serta riset terbaik.</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B21)</f>
+        <f>COUNTA(Anggota!B5:B22)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F21)</f>
+        <f>COUNTA(Anggota!F5:F22)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,12 +913,12 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Ridwan Syam, S.Sos, M.Si</t>
+          <t>Dr. Muh. Iqbal Latif, M.Si</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
@@ -926,19 +926,19 @@
           <t>Hasanuddin University</t>
         </is>
       </c>
-      <c r="E5" s="11" t="n"/>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>Political Sociology, Social Policy, and Social Behavior</t>
+        </is>
+      </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
-      <c r="J5" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-6182-7162</t>
-        </is>
-      </c>
+      <c r="J5" s="12" t="n"/>
       <c r="K5" s="11" t="inlineStr">
         <is>
-          <t>6782484</t>
+          <t>6670258</t>
         </is>
       </c>
       <c r="L5" s="12" t="n"/>
@@ -954,36 +954,32 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Novia Fridayanti, M.Si.</t>
+          <t>Ridwan Syam, S.Sos, M.Si</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Cultural Sociology and Livelihood Studies</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
           <t>Hasanuddin University</t>
         </is>
       </c>
+      <c r="E6" s="11" t="n"/>
       <c r="F6" s="12" t="n"/>
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="12" t="n"/>
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>0009-0009-4242-9845</t>
+          <t>0000-0002-6182-7162</t>
         </is>
       </c>
       <c r="K6" s="11" t="inlineStr">
         <is>
-          <t>6941674</t>
+          <t>6782484</t>
         </is>
       </c>
       <c r="L6" s="12" t="n"/>
@@ -999,30 +995,38 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dr. Wengki Ariando</t>
+          <t>Novia Fridayanti, M.Si.</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Political Ecology, Customary Communities, Coastal Resource Management, and Climate Change Adaptation</t>
+          <t>Cultural Sociology and Livelihood Studies</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>KITVL - Royal Netherlands Institute of Southeast Asian and Carribean Studies</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="12" t="n"/>
       <c r="I7" s="12" t="n"/>
-      <c r="J7" s="12" t="n"/>
-      <c r="K7" s="12" t="n"/>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>0009-0009-4242-9845</t>
+        </is>
+      </c>
+      <c r="K7" s="11" t="inlineStr">
+        <is>
+          <t>6941674</t>
+        </is>
+      </c>
       <c r="L7" s="12" t="n"/>
       <c r="M7" s="11" t="inlineStr">
         <is>
@@ -1036,16 +1040,24 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Fatmawati</t>
+          <t>Dr. Wengki Ariando</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="n"/>
-      <c r="E8" s="11" t="n"/>
+          <t>External collaborator</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>Political Ecology, Customary Communities, Coastal Resource Management, and Climate Change Adaptation</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>KITVL - Royal Netherlands Institute of Southeast Asian and Carribean Studies</t>
+        </is>
+      </c>
       <c r="F8" s="12" t="n"/>
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="12" t="n"/>
@@ -1065,12 +1077,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Lalu Ahmalian Bahari</t>
+          <t>Fatmawati</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D9" s="12" t="n"/>
@@ -1092,10 +1104,22 @@
       <c r="A10" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="12" t="n"/>
-      <c r="C10" s="12" t="n"/>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>Lalu Ahmalian Bahari</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
       <c r="D10" s="12" t="n"/>
-      <c r="E10" s="11" t="n"/>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>The Public Opinion and Social Behavior Research Group is established as an interdisciplinary research platform dedicated to understanding how public opinion is formed, expressed, and transformed into social behavior across digital and offline contexts.</t>
+        </is>
+      </c>
       <c r="F10" s="12" t="n"/>
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="12" t="n"/>
@@ -1103,7 +1127,11 @@
       <c r="J10" s="12" t="n"/>
       <c r="K10" s="12" t="n"/>
       <c r="L10" s="12" t="n"/>
-      <c r="M10" s="12" t="n"/>
+      <c r="M10" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -1292,15 +1320,32 @@
       <c r="L21" s="12" t="n"/>
       <c r="M21" s="12" t="n"/>
     </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="12" t="n"/>
+      <c r="C22" s="12" t="n"/>
+      <c r="D22" s="12" t="n"/>
+      <c r="E22" s="11" t="n"/>
+      <c r="F22" s="12" t="n"/>
+      <c r="G22" s="12" t="n"/>
+      <c r="H22" s="12" t="n"/>
+      <c r="I22" s="12" t="n"/>
+      <c r="J22" s="12" t="n"/>
+      <c r="K22" s="12" t="n"/>
+      <c r="L22" s="12" t="n"/>
+      <c r="M22" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
